--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104462_W1.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104462_W1.xlsx
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.3371</v>
+        <v>5.3799</v>
       </c>
       <c r="E2" t="n">
-        <v>2.4805</v>
+        <v>1.9967</v>
       </c>
       <c r="F2" t="n">
-        <v>3.8566</v>
+        <v>3.3833</v>
       </c>
       <c r="G2" t="n">
-        <v>4.5539</v>
+        <v>4.5524</v>
       </c>
       <c r="H2" t="n">
-        <v>4.1833</v>
+        <v>4.1737</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3706</v>
+        <v>0.3787</v>
       </c>
       <c r="J2" t="n">
-        <v>2.6233</v>
+        <v>2.5976</v>
       </c>
       <c r="K2" t="n">
-        <v>3.335</v>
+        <v>3.3127</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.7117</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>1.9306</v>
+        <v>1.9548</v>
       </c>
       <c r="N2" t="n">
-        <v>0.8483000000000001</v>
+        <v>0.8609</v>
       </c>
       <c r="O2" t="n">
-        <v>1.0823</v>
+        <v>1.0939</v>
       </c>
       <c r="P2" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.8147</v>
+        <v>-1.8211</v>
       </c>
       <c r="R2" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S2" t="n">
-        <v>1.8074</v>
+        <v>0.8574000000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>0.9648</v>
+        <v>0.5177</v>
       </c>
       <c r="U2" t="n">
-        <v>0.8426</v>
+        <v>0.3397</v>
       </c>
       <c r="V2" t="n">
-        <v>1.3369</v>
+        <v>1.3359</v>
       </c>
       <c r="W2" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="X2" t="n">
-        <v>0.6298</v>
+        <v>0.6334</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. EJIM</t>
+          <t>C. AGADA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.57</v>
+        <v>3.0202</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.1023</v>
+        <v>2.1039</v>
       </c>
       <c r="F3" t="n">
-        <v>3.6723</v>
+        <v>0.9163</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8508</v>
+        <v>5.4976</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.8179</v>
+        <v>1.4055</v>
       </c>
       <c r="I3" t="n">
-        <v>1.6687</v>
+        <v>4.0921</v>
       </c>
       <c r="J3" t="n">
-        <v>-1.4612</v>
+        <v>3.3717</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.7916</v>
+        <v>1.2196</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3304</v>
+        <v>2.1521</v>
       </c>
       <c r="M3" t="n">
-        <v>2.312</v>
+        <v>2.1259</v>
       </c>
       <c r="N3" t="n">
-        <v>0.9737</v>
+        <v>0.1859</v>
       </c>
       <c r="O3" t="n">
-        <v>1.3382</v>
+        <v>1.94</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6805</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1342</v>
+        <v>-1.5934</v>
       </c>
       <c r="R3" t="n">
-        <v>1.8147</v>
+        <v>1.3658</v>
       </c>
       <c r="S3" t="n">
-        <v>1.7173</v>
+        <v>0.4566</v>
       </c>
       <c r="T3" t="n">
-        <v>2.1716</v>
+        <v>0.7126</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4543</v>
+        <v>-0.256</v>
       </c>
       <c r="V3" t="n">
-        <v>0.3214</v>
+        <v>-2.7064</v>
       </c>
       <c r="W3" t="n">
-        <v>0.3214</v>
+        <v>-0.387</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-2.3194</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C. AGADA</t>
+          <t>M. EJIM</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.2351</v>
+        <v>2.5778</v>
       </c>
       <c r="E4" t="n">
-        <v>2.1974</v>
+        <v>-1.19</v>
       </c>
       <c r="F4" t="n">
-        <v>1.0377</v>
+        <v>3.7677</v>
       </c>
       <c r="G4" t="n">
-        <v>5.5134</v>
+        <v>0.8381999999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>1.4245</v>
+        <v>-0.8348</v>
       </c>
       <c r="I4" t="n">
-        <v>4.0889</v>
+        <v>1.673</v>
       </c>
       <c r="J4" t="n">
-        <v>3.4147</v>
+        <v>-1.505</v>
       </c>
       <c r="K4" t="n">
-        <v>1.253</v>
+        <v>-1.8248</v>
       </c>
       <c r="L4" t="n">
-        <v>2.1617</v>
+        <v>0.3198</v>
       </c>
       <c r="M4" t="n">
-        <v>2.0988</v>
+        <v>2.3432</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1715</v>
+        <v>0.99</v>
       </c>
       <c r="O4" t="n">
-        <v>1.9273</v>
+        <v>1.3532</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.2268</v>
+        <v>0.6829</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.5878</v>
+        <v>-1.1382</v>
       </c>
       <c r="R4" t="n">
-        <v>1.361</v>
+        <v>1.8211</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6608000000000001</v>
+        <v>0.7411</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7561</v>
+        <v>1.1377</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0953</v>
+        <v>-0.3965</v>
       </c>
       <c r="V4" t="n">
-        <v>-2.7124</v>
+        <v>0.3155</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.3856</v>
+        <v>0.3155</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.3267</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>C. KRUTWIG</t>
+          <t>A. DIAGNE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.6729</v>
+        <v>1.976</v>
       </c>
       <c r="E5" t="n">
-        <v>2.3514</v>
+        <v>1.3588</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3215</v>
+        <v>0.6172</v>
       </c>
       <c r="G5" t="n">
-        <v>0.983</v>
+        <v>1.293</v>
       </c>
       <c r="H5" t="n">
-        <v>1.6147</v>
+        <v>0.7267</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.6317</v>
+        <v>0.5662</v>
       </c>
       <c r="J5" t="n">
-        <v>1.737</v>
+        <v>0.79</v>
       </c>
       <c r="K5" t="n">
-        <v>1.6624</v>
+        <v>0.641</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0746</v>
+        <v>0.1489</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.754</v>
+        <v>0.503</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0477</v>
+        <v>0.0857</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.7063</v>
+        <v>0.4173</v>
       </c>
       <c r="P5" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S5" t="n">
-        <v>1.1662</v>
+        <v>0.7921</v>
       </c>
       <c r="T5" t="n">
-        <v>1.2249</v>
+        <v>0.5688</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0587</v>
+        <v>0.2232</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.6105</v>
+        <v>-1.2472</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.6105</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. DIAGNE</t>
+          <t>C. KRUTWIG</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.4815</v>
+        <v>1.9192</v>
       </c>
       <c r="E6" t="n">
-        <v>1.886</v>
+        <v>1.7725</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5956</v>
+        <v>0.1467</v>
       </c>
       <c r="G6" t="n">
-        <v>1.2912</v>
+        <v>0.9861</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7287</v>
+        <v>1.6114</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5625</v>
+        <v>-0.6254</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8002</v>
+        <v>1.7292</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6509</v>
+        <v>1.6547</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1493</v>
+        <v>0.0745</v>
       </c>
       <c r="M6" t="n">
-        <v>0.491</v>
+        <v>-0.7432</v>
       </c>
       <c r="N6" t="n">
-        <v>0.07779999999999999</v>
+        <v>-0.0433</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4132</v>
+        <v>-0.6998</v>
       </c>
       <c r="P6" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S6" t="n">
-        <v>1.3096</v>
+        <v>0.4112</v>
       </c>
       <c r="T6" t="n">
-        <v>1.0858</v>
+        <v>0.6595</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2238</v>
+        <v>-0.2483</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.2534</v>
+        <v>-0.6162</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>-0.6162</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.2534</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. SANZ</t>
+          <t>J. BATEMON</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6196</v>
+        <v>1.6714</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.6591</v>
+        <v>-1.1112</v>
       </c>
       <c r="F7" t="n">
-        <v>2.2787</v>
+        <v>2.7826</v>
       </c>
       <c r="G7" t="n">
-        <v>0.97</v>
+        <v>3.3101</v>
       </c>
       <c r="H7" t="n">
-        <v>2.1269</v>
+        <v>1.6627</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.1568</v>
+        <v>1.6474</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9026</v>
+        <v>1.8855</v>
       </c>
       <c r="K7" t="n">
-        <v>1.7663</v>
+        <v>0.4859</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.8637</v>
+        <v>1.3997</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0674</v>
+        <v>1.4245</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3605</v>
+        <v>1.1768</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.2931</v>
+        <v>0.2477</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.2268</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.8147</v>
+        <v>-3.6421</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0178</v>
+        <v>0.4101</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.747</v>
+        <v>0.6454</v>
       </c>
       <c r="U7" t="n">
-        <v>0.7649</v>
+        <v>-0.2353</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.1414</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.1414</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. BATEMON</t>
+          <t>M. SANZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0193</v>
+        <v>1.4506</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.3295</v>
+        <v>-0.575</v>
       </c>
       <c r="F8" t="n">
-        <v>2.3489</v>
+        <v>2.0255</v>
       </c>
       <c r="G8" t="n">
-        <v>3.3078</v>
+        <v>0.9765</v>
       </c>
       <c r="H8" t="n">
-        <v>1.6579</v>
+        <v>2.1309</v>
       </c>
       <c r="I8" t="n">
-        <v>1.6499</v>
+        <v>-1.1543</v>
       </c>
       <c r="J8" t="n">
-        <v>1.9077</v>
+        <v>0.8864</v>
       </c>
       <c r="K8" t="n">
-        <v>0.4951</v>
+        <v>1.7582</v>
       </c>
       <c r="L8" t="n">
-        <v>1.4126</v>
+        <v>-0.8718</v>
       </c>
       <c r="M8" t="n">
-        <v>1.4001</v>
+        <v>0.0901</v>
       </c>
       <c r="N8" t="n">
-        <v>1.1628</v>
+        <v>0.3727</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2373</v>
+        <v>-0.2826</v>
       </c>
       <c r="P8" t="n">
-        <v>-2.0415</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.6293</v>
+        <v>-1.8211</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.247</v>
+        <v>0.8421999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6079</v>
+        <v>0.3597</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.6391</v>
+        <v>0.4824</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.1405</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.1405</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>K. ZORIKS</t>
+          <t>M. JIMENEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0072</v>
+        <v>0.6165</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.5841</v>
+        <v>-0.7995</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5913</v>
+        <v>1.4159</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.2678</v>
+        <v>0.9482</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6839</v>
+        <v>0.8558</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.9516</v>
+        <v>0.0924</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.2448</v>
+        <v>-0.6342</v>
       </c>
       <c r="K9" t="n">
-        <v>0.5124</v>
+        <v>0.4686</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.7572</v>
+        <v>-1.1029</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.023</v>
+        <v>1.5825</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1715</v>
+        <v>0.3871</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.1945</v>
+        <v>1.1953</v>
       </c>
       <c r="P9" t="n">
-        <v>1.5878</v>
+        <v>0.2276</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.2268</v>
+        <v>-0.4553</v>
       </c>
       <c r="R9" t="n">
-        <v>1.8147</v>
+        <v>0.6829</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1561</v>
+        <v>-0.2611</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0484</v>
+        <v>0.29</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1077</v>
+        <v>-0.5512</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.1568</v>
+        <v>-0.2983</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.06419999999999999</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.0927</v>
+        <v>-0.2983</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. JIMENEZ</t>
+          <t>K. ZORIKS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.6919999999999999</v>
+        <v>0.1606</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.6741</v>
+        <v>-0.3393</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9821</v>
+        <v>0.4999</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9448</v>
+        <v>-0.2675</v>
       </c>
       <c r="H10" t="n">
-        <v>0.8542</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0906</v>
+        <v>-0.9566</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.6125</v>
+        <v>-0.2723</v>
       </c>
       <c r="K10" t="n">
-        <v>0.4778</v>
+        <v>0.5031</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.0903</v>
+        <v>-0.7754</v>
       </c>
       <c r="M10" t="n">
-        <v>1.5574</v>
+        <v>0.0048</v>
       </c>
       <c r="N10" t="n">
-        <v>0.3764</v>
+        <v>0.1859</v>
       </c>
       <c r="O10" t="n">
-        <v>1.1809</v>
+        <v>-0.1811</v>
       </c>
       <c r="P10" t="n">
-        <v>0.2268</v>
+        <v>1.5934</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.4537</v>
+        <v>-0.2276</v>
       </c>
       <c r="R10" t="n">
-        <v>0.6805</v>
+        <v>1.8211</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.5615</v>
+        <v>-0.0044</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6079</v>
+        <v>0.232</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.9536</v>
+        <v>-0.2364</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.3021</v>
+        <v>-1.1609</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>-0.07140000000000001</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.3021</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.0845</v>
+        <v>-0.7187</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.9143</v>
+        <v>-1.6666</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8298</v>
+        <v>0.9479</v>
       </c>
       <c r="G11" t="n">
-        <v>0.309</v>
+        <v>0.3124</v>
       </c>
       <c r="H11" t="n">
-        <v>0.8528</v>
+        <v>0.853</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5437</v>
+        <v>-0.5406</v>
       </c>
       <c r="J11" t="n">
-        <v>0.828</v>
+        <v>0.8119</v>
       </c>
       <c r="K11" t="n">
-        <v>0.9799</v>
+        <v>0.9685</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.152</v>
+        <v>-0.1566</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.5189</v>
+        <v>-0.4995</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.1272</v>
+        <v>-0.1155</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.3918</v>
+        <v>-0.384</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.8562</v>
+        <v>-3.8697</v>
       </c>
       <c r="R11" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1503</v>
+        <v>0.5239</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0212</v>
+        <v>0.3017</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1291</v>
+        <v>0.2221</v>
       </c>
       <c r="V11" t="n">
-        <v>0.9513</v>
+        <v>0.949</v>
       </c>
       <c r="W11" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.1414</v>
+        <v>-0.1405</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.8183</v>
+        <v>-0.9756</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.8915999999999999</v>
+        <v>-0.3532</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.9266</v>
+        <v>-0.6224</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6632</v>
+        <v>0.6535</v>
       </c>
       <c r="H12" t="n">
-        <v>1.8787</v>
+        <v>1.8784</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.2156</v>
+        <v>-1.2249</v>
       </c>
       <c r="J12" t="n">
-        <v>0.8867</v>
+        <v>0.8663</v>
       </c>
       <c r="K12" t="n">
-        <v>1.4546</v>
+        <v>1.4479</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.5679</v>
+        <v>-0.5816</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.2236</v>
+        <v>-0.2129</v>
       </c>
       <c r="N12" t="n">
-        <v>0.4241</v>
+        <v>0.4305</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.6477000000000001</v>
+        <v>-0.6433</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R12" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3868</v>
+        <v>0.4588</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4174</v>
+        <v>0.1462</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0305</v>
+        <v>0.3126</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.4141</v>
+        <v>-1.405</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.4141</v>
+        <v>-1.405</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>15.3479</v>
+        <v>17.0779</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.2397000000000005</v>
+        <v>1.1971</v>
       </c>
       <c r="F13" t="n">
-        <v>15.5879</v>
+        <v>15.8806</v>
       </c>
       <c r="G13" t="n">
-        <v>19.1193</v>
+        <v>19.1005</v>
       </c>
       <c r="H13" t="n">
-        <v>15.1877</v>
+        <v>15.1523</v>
       </c>
       <c r="I13" t="n">
-        <v>3.931799999999999</v>
+        <v>3.948</v>
       </c>
       <c r="J13" t="n">
-        <v>10.7817</v>
+        <v>10.5271</v>
       </c>
       <c r="K13" t="n">
-        <v>10.7958</v>
+        <v>10.6354</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.01419999999999999</v>
+        <v>-0.1084999999999997</v>
       </c>
       <c r="M13" t="n">
-        <v>8.3378</v>
+        <v>8.5732</v>
       </c>
       <c r="N13" t="n">
-        <v>4.3917</v>
+        <v>4.5167</v>
       </c>
       <c r="O13" t="n">
-        <v>3.945800000000001</v>
+        <v>4.0566</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.2683</v>
+        <v>-2.2762</v>
       </c>
       <c r="Q13" t="n">
-        <v>-15.8784</v>
+        <v>-15.9343</v>
       </c>
       <c r="R13" t="n">
-        <v>13.6101</v>
+        <v>13.6581</v>
       </c>
       <c r="S13" t="n">
-        <v>3.478</v>
+        <v>5.2279</v>
       </c>
       <c r="T13" t="n">
-        <v>3.795800000000001</v>
+        <v>5.571300000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3178</v>
+        <v>-0.3437000000000001</v>
       </c>
       <c r="V13" t="n">
-        <v>-4.981100000000001</v>
+        <v>-4.9741</v>
       </c>
       <c r="W13" t="n">
-        <v>1.0609</v>
+        <v>1.0329</v>
       </c>
       <c r="X13" t="n">
-        <v>-6.042</v>
+        <v>-6.007000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.2333</v>
+        <v>2.346</v>
       </c>
       <c r="E14" t="n">
-        <v>1.6792</v>
+        <v>1.6285</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5541</v>
+        <v>0.7175</v>
       </c>
       <c r="G14" t="n">
-        <v>-4.4492</v>
+        <v>-4.4519</v>
       </c>
       <c r="H14" t="n">
-        <v>-2.5166</v>
+        <v>-2.5105</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.9326</v>
+        <v>-1.9414</v>
       </c>
       <c r="J14" t="n">
-        <v>-3.0568</v>
+        <v>-3.0921</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.4759</v>
+        <v>-1.4898</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.5808</v>
+        <v>-1.6023</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.3924</v>
+        <v>-1.3598</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.0407</v>
+        <v>-1.0207</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.3517</v>
+        <v>-0.3391</v>
       </c>
       <c r="P14" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.5955</v>
+        <v>-0.4705</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.3417</v>
+        <v>-0.3397</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2538</v>
+        <v>-0.1308</v>
       </c>
       <c r="V14" t="n">
-        <v>5.4633</v>
+        <v>5.4474</v>
       </c>
       <c r="W14" t="n">
-        <v>5.0777</v>
+        <v>5.0604</v>
       </c>
       <c r="X14" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="15">
@@ -1579,58 +1579,58 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.8223</v>
+        <v>1.085</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.1461</v>
+        <v>-0.6221</v>
       </c>
       <c r="F15" t="n">
-        <v>1.9684</v>
+        <v>1.7071</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.0994</v>
+        <v>-0.08799999999999999</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.0751</v>
+        <v>-1.0715</v>
       </c>
       <c r="I15" t="n">
-        <v>0.9756</v>
+        <v>0.9835</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.3427</v>
+        <v>-0.3477</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.492</v>
+        <v>-0.4966</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1493</v>
+        <v>0.1489</v>
       </c>
       <c r="M15" t="n">
-        <v>0.2433</v>
+        <v>0.2597</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.5831</v>
+        <v>-0.5749</v>
       </c>
       <c r="O15" t="n">
-        <v>0.8264</v>
+        <v>0.8345</v>
       </c>
       <c r="P15" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5607</v>
+        <v>-0.1928</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1966</v>
+        <v>-0.2744</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3641</v>
+        <v>0.08160000000000001</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.1765</v>
+        <v>0.3224</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.3408</v>
+        <v>-1.0584</v>
       </c>
       <c r="F16" t="n">
-        <v>1.5173</v>
+        <v>1.3807</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.0963</v>
+        <v>-1.0914</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.808</v>
+        <v>-1.8066</v>
       </c>
       <c r="I16" t="n">
-        <v>0.7117</v>
+        <v>0.7151999999999999</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.5374</v>
+        <v>-0.547</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.2091</v>
+        <v>-1.2173</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6717</v>
+        <v>0.6703</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.5590000000000001</v>
+        <v>-0.5444</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.599</v>
+        <v>-0.5893</v>
       </c>
       <c r="O16" t="n">
-        <v>0.04</v>
+        <v>0.0449</v>
       </c>
       <c r="P16" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R16" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S16" t="n">
-        <v>1.2748</v>
+        <v>0.4122</v>
       </c>
       <c r="T16" t="n">
-        <v>1.3308</v>
+        <v>0.6268</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.056</v>
+        <v>-0.2146</v>
       </c>
       <c r="V16" t="n">
-        <v>0.7712</v>
+        <v>0.7739</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0.7712</v>
+        <v>0.7739</v>
       </c>
     </row>
     <row r="17">
@@ -1735,58 +1735,58 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2601</v>
+        <v>0.2811</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.9888</v>
+        <v>-0.6577</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7287</v>
+        <v>0.9388</v>
       </c>
       <c r="G17" t="n">
-        <v>0.4857</v>
+        <v>0.4856</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.3348</v>
+        <v>-1.33</v>
       </c>
       <c r="I17" t="n">
-        <v>1.8205</v>
+        <v>1.8156</v>
       </c>
       <c r="J17" t="n">
-        <v>0.8924</v>
+        <v>0.8733</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1141</v>
+        <v>0.1067</v>
       </c>
       <c r="L17" t="n">
-        <v>0.7782</v>
+        <v>0.7665999999999999</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.4066</v>
+        <v>-0.3877</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.4489</v>
+        <v>-1.4367</v>
       </c>
       <c r="O17" t="n">
-        <v>1.0423</v>
+        <v>1.049</v>
       </c>
       <c r="P17" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.1995</v>
+        <v>-0.6597</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.747</v>
+        <v>-0.3929</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4525</v>
+        <v>-0.2669</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.4791</v>
+        <v>-0.253</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.0762</v>
+        <v>-0.8716</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5971</v>
+        <v>0.6186</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.1942</v>
+        <v>-0.1965</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.0014</v>
+        <v>-2.0018</v>
       </c>
       <c r="I18" t="n">
-        <v>1.8072</v>
+        <v>1.8053</v>
       </c>
       <c r="J18" t="n">
-        <v>0.338</v>
+        <v>0.3203</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.7415</v>
+        <v>-0.7519</v>
       </c>
       <c r="L18" t="n">
-        <v>1.0795</v>
+        <v>1.0722</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.5321</v>
+        <v>-0.5168</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.2599</v>
+        <v>-1.2499</v>
       </c>
       <c r="O18" t="n">
-        <v>0.7277</v>
+        <v>0.7331</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.6291</v>
+        <v>-0.3948</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3992</v>
+        <v>-0.1628</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2299</v>
+        <v>-0.232</v>
       </c>
       <c r="V18" t="n">
-        <v>1.4783</v>
+        <v>1.4764</v>
       </c>
       <c r="W18" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="X18" t="n">
-        <v>0.2249</v>
+        <v>0.2292</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. DREZNJAK</t>
+          <t>B. DIBBA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.0936</v>
+        <v>-0.6973</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.1702</v>
+        <v>-0.447</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.9234</v>
+        <v>-0.2503</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.7195</v>
+        <v>-0.255</v>
       </c>
       <c r="H19" t="n">
-        <v>0.9465</v>
+        <v>-0.526</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.6659</v>
+        <v>0.271</v>
       </c>
       <c r="J19" t="n">
-        <v>0.519</v>
+        <v>0.6338</v>
       </c>
       <c r="K19" t="n">
-        <v>1.42</v>
+        <v>1.1409</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.901</v>
+        <v>-0.5071</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.2384</v>
+        <v>-0.8888</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4735</v>
+        <v>-1.6668</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.7649</v>
+        <v>0.778</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>0.9105</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1342</v>
+        <v>2.0487</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3741</v>
+        <v>-0.4926</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2843</v>
+        <v>-0.1004</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.6584</v>
+        <v>-0.3921</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-0.8603</v>
       </c>
       <c r="W19" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.1607</v>
+        <v>-1.018</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>B. DIBBA</t>
+          <t>D. DREZNJAK</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.173</v>
+        <v>-0.9853</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.5343</v>
+        <v>-0.3069</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.6387</v>
+        <v>-0.6784</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.258</v>
+        <v>-0.7122000000000001</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.5326</v>
+        <v>0.9532</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2745</v>
+        <v>-1.6654</v>
       </c>
       <c r="J20" t="n">
-        <v>0.6599</v>
+        <v>0.5044</v>
       </c>
       <c r="K20" t="n">
-        <v>1.1531</v>
+        <v>1.4134</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.4932</v>
+        <v>-0.909</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.9179</v>
+        <v>-1.2166</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.6857</v>
+        <v>-0.4603</v>
       </c>
       <c r="O20" t="n">
-        <v>0.7678</v>
+        <v>-0.7563</v>
       </c>
       <c r="P20" t="n">
-        <v>0.9073</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R20" t="n">
-        <v>2.0415</v>
+        <v>1.1382</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.9545</v>
+        <v>-0.2731</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2208</v>
+        <v>0.1691</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.7337</v>
+        <v>-0.4422</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.8678</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.0285</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. BRANKOVIC</t>
+          <t>A. ARANITOVIC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.1478</v>
+        <v>-3.238</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.7647</v>
+        <v>-2.5007</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.3831</v>
+        <v>-0.7373</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.2474</v>
+        <v>-2.477</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.4211</v>
+        <v>-1.7721</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.8263</v>
+        <v>-0.7049</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.4067</v>
+        <v>-1.7314</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.444</v>
+        <v>-0.6657</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0373</v>
+        <v>-1.0656</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.8407</v>
+        <v>-0.7457</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.9771</v>
+        <v>-1.1064</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.8636</v>
+        <v>0.3608</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.8147</v>
+        <v>0.2276</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.2683</v>
+        <v>-1.1382</v>
       </c>
       <c r="R21" t="n">
-        <v>0.4537</v>
+        <v>1.3658</v>
       </c>
       <c r="S21" t="n">
-        <v>1.6855</v>
+        <v>-0.0569</v>
       </c>
       <c r="T21" t="n">
-        <v>1.6816</v>
+        <v>0.2111</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0039</v>
+        <v>-0.268</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.7712</v>
+        <v>-0.9317</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.7712</v>
+        <v>0.1578</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. ARANITOVIC</t>
+          <t>D. RUSSELL</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.4791</v>
+        <v>-4.2755</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.0624</v>
+        <v>-4.2203</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.4167</v>
+        <v>-0.0552</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.4718</v>
+        <v>-4.7049</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.7734</v>
+        <v>-3.0845</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.6984</v>
+        <v>-1.6205</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.7079</v>
+        <v>-3.1163</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.6549</v>
+        <v>-2.2073</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.053</v>
+        <v>-0.909</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.7639</v>
+        <v>-1.5886</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.1185</v>
+        <v>-0.8772</v>
       </c>
       <c r="O22" t="n">
-        <v>0.3546</v>
+        <v>-0.7114</v>
       </c>
       <c r="P22" t="n">
-        <v>0.2268</v>
+        <v>0.9105</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R22" t="n">
-        <v>1.361</v>
+        <v>2.0487</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3021</v>
+        <v>-0.4811</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3811</v>
+        <v>0.0341</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0789</v>
+        <v>-0.5152</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.9320000000000001</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0.1607</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>D. RUSSELL</t>
+          <t>D. BRANKOVIC</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,64 +2203,64 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.0431</v>
+        <v>-4.4336</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.5416</v>
+        <v>-2.9767</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.5016</v>
+        <v>-1.4569</v>
       </c>
       <c r="G23" t="n">
-        <v>-4.708</v>
+        <v>-2.2531</v>
       </c>
       <c r="H23" t="n">
-        <v>-3.0821</v>
+        <v>-1.4325</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.6259</v>
+        <v>-0.8205</v>
       </c>
       <c r="J23" t="n">
-        <v>-3.0838</v>
+        <v>-0.4324</v>
       </c>
       <c r="K23" t="n">
-        <v>-2.1828</v>
+        <v>-0.4696</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.901</v>
+        <v>0.0372</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.6242</v>
+        <v>-1.8207</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.8993</v>
+        <v>-0.9629</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.7249</v>
+        <v>-0.8578</v>
       </c>
       <c r="P23" t="n">
-        <v>0.9073</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.1342</v>
+        <v>-2.2763</v>
       </c>
       <c r="R23" t="n">
-        <v>2.0415</v>
+        <v>0.4553</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.2424</v>
+        <v>0.4144</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3236</v>
+        <v>0.506</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.9188</v>
+        <v>-0.0915</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>-0.7739</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>-0.7739</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.9044</v>
+        <v>-4.6973</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.6421</v>
+        <v>-3.8478</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.2623</v>
+        <v>-0.8495</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.3613</v>
+        <v>-3.3559</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.589</v>
+        <v>-0.5697</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.7723</v>
+        <v>-2.7862</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.6116</v>
+        <v>-1.6382</v>
       </c>
       <c r="K24" t="n">
-        <v>0.1212</v>
+        <v>0.1207</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.7328</v>
+        <v>-1.7589</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.7497</v>
+        <v>-1.7177</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.7103</v>
+        <v>-0.6904</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.0395</v>
+        <v>-1.0273</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R24" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.7018</v>
+        <v>-0.5007</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.7621</v>
+        <v>0.0668</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.9397</v>
+        <v>-0.5675</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-15.3481</v>
+        <v>-14.5455</v>
       </c>
       <c r="E25" t="n">
-        <v>-15.588</v>
+        <v>-15.8807</v>
       </c>
       <c r="F25" t="n">
-        <v>0.2397999999999998</v>
+        <v>1.3351</v>
       </c>
       <c r="G25" t="n">
-        <v>-19.1194</v>
+        <v>-19.1003</v>
       </c>
       <c r="H25" t="n">
-        <v>-15.1876</v>
+        <v>-15.152</v>
       </c>
       <c r="I25" t="n">
-        <v>-3.9319</v>
+        <v>-3.9483</v>
       </c>
       <c r="J25" t="n">
-        <v>-8.3376</v>
+        <v>-8.5733</v>
       </c>
       <c r="K25" t="n">
-        <v>-4.3918</v>
+        <v>-4.5165</v>
       </c>
       <c r="L25" t="n">
-        <v>-3.9458</v>
+        <v>-4.0567</v>
       </c>
       <c r="M25" t="n">
-        <v>-10.7816</v>
+        <v>-10.5271</v>
       </c>
       <c r="N25" t="n">
-        <v>-10.796</v>
+        <v>-10.6355</v>
       </c>
       <c r="O25" t="n">
-        <v>0.01419999999999999</v>
+        <v>0.1083999999999998</v>
       </c>
       <c r="P25" t="n">
-        <v>2.2682</v>
+        <v>2.2762</v>
       </c>
       <c r="Q25" t="n">
-        <v>-13.6101</v>
+        <v>-13.6581</v>
       </c>
       <c r="R25" t="n">
-        <v>15.8784</v>
+        <v>15.9344</v>
       </c>
       <c r="S25" t="n">
-        <v>-3.478</v>
+        <v>-2.6956</v>
       </c>
       <c r="T25" t="n">
-        <v>0.3177999999999999</v>
+        <v>0.3437</v>
       </c>
       <c r="U25" t="n">
-        <v>-3.7959</v>
+        <v>-3.0392</v>
       </c>
       <c r="V25" t="n">
-        <v>4.9811</v>
+        <v>4.974</v>
       </c>
       <c r="W25" t="n">
-        <v>6.042000000000001</v>
+        <v>6.007099999999999</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.0609</v>
+        <v>-1.033</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104462_W1.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104462_W1.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0.6334</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104462_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-2.3194</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104462_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104462_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104462_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104462_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104462_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-0.1405</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104462_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-0.2983</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104462_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104462_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-0.1405</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104462_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-1.405</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104462_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-6.007000000000001</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104462_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104462_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0.7739</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104462_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104462_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0.2292</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104462_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-1.018</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104462_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104462_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104462_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>0</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104462_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>0</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104462_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104462_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,7 @@
       <c r="X25" t="n">
         <v>-1.033</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
